--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2064,6 +2064,117 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115112531</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562494</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6464920</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>113544064</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>115262867</v>
       </c>
       <c r="B15" t="n">
-        <v>57316</v>
+        <v>57326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -2180,7 +2180,7 @@
         <v>115262867</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>57484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -2180,7 +2180,7 @@
         <v>115262867</v>
       </c>
       <c r="B15" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113349339</v>
+        <v>113398077</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
+        <v>57414</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,45 +1602,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562513</v>
+        <v>562543</v>
       </c>
       <c r="R10" t="n">
-        <v>6464945</v>
+        <v>6464911</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,19 +1666,19 @@
           <t>Björsäter</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>E-Åtv-0251</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1693,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1697,15 +1701,11 @@
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113398077</v>
+        <v>113544135</v>
       </c>
       <c r="B11" t="n">
         <v>57414</v>
@@ -1745,7 +1745,11 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1753,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562543</v>
+        <v>562506</v>
       </c>
       <c r="R11" t="n">
-        <v>6464911</v>
+        <v>6464936</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,17 +1787,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+          <t>Paret som har sitt häckningsrevir och födosöksområde i området och I anslutning till torpet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113544135</v>
+        <v>115112531</v>
       </c>
       <c r="B12" t="n">
-        <v>57414</v>
+        <v>97650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,50 +1836,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Risten, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562506</v>
+        <v>562494</v>
       </c>
       <c r="R12" t="n">
-        <v>6464936</v>
+        <v>6464920</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,17 +1902,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Paret som har sitt häckningsrevir och födosöksområde i området och I anslutning till torpet.</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,6 +1916,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1939,58 +1935,70 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115112531</v>
+        <v>113544064</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562494</v>
+        <v>562522</v>
       </c>
       <c r="R13" t="n">
-        <v>6464920</v>
+        <v>6464930</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2017,12 +2025,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hanen som har revir och födosöksområde i reservatsförslaget. Den brukar ses och höras i området nästan dagligen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2044,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2050,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113544064</v>
+        <v>115262867</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,16 +2078,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2088,11 +2100,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>hane</t>
@@ -2100,20 +2108,24 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562522</v>
+        <v>562492</v>
       </c>
       <c r="R14" t="n">
-        <v>6464930</v>
+        <v>6464939</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2140,17 +2152,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hanen som har revir och födosöksområde i reservatsförslaget. Den brukar ses och höras i området nästan dagligen.</t>
+          <t>Observerades inom häckningsrevir. De har börjat ifjol att häcka i området och dra upp en kull med ungar men nu hugger Södra myndigheternas goda mina bort viktigq delar av häckningsreviret.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,133 +2186,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>115262867</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Risten , Ög</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>562492</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6464939</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Björsäter</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Observerades inom häckningsrevir. De har börjat ifjol att häcka i området och dra upp en kull med ungar men nu hugger Södra myndigheternas goda mina bort viktigq delar av häckningsreviret.</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92456297</v>
+        <v>68489160</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>786</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åtvidaberg, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562522.9380247607</v>
+        <v>562470</v>
       </c>
       <c r="R2" t="n">
-        <v>6464941.412404787</v>
+        <v>6464970</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,27 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår, äldre. Idag liggande träd.</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,79 +756,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110631484</v>
+        <v>114920113</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562513.4000622773</v>
+        <v>562475</v>
       </c>
       <c r="R3" t="n">
-        <v>6464945.463927539</v>
+        <v>6464913</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +876,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110908846</v>
+        <v>113398085</v>
       </c>
       <c r="B4" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,41 +887,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562511.4718256755</v>
+        <v>562463</v>
       </c>
       <c r="R4" t="n">
-        <v>6464967.497646832</v>
+        <v>6464958</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +962,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,43 +981,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113249042</v>
+        <v>113398082</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,13 +1019,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562536</v>
+        <v>562455</v>
       </c>
       <c r="R5" t="n">
-        <v>6464923</v>
+        <v>6464953</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,17 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde som Södra tänker avverka. Gång på gång har man avverkad I reviret under falska förespeglingar om akuta barkborreangrepp men när man hugger på vintern finns inga  barkborrar längre i träden.</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1063,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,43 +1082,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113248944</v>
+        <v>122700413</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1124,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562513</v>
+        <v>562550</v>
       </c>
       <c r="R6" t="n">
-        <v>6464940</v>
+        <v>6464935</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,17 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Inne i av Södra planerad avverkningsanmälnan A37222-2023. Skoglig värdekärna klassat som V1 av Länsstyrelsen.</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113248919</v>
+        <v>122700414</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,27 +1198,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,13 +1229,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562513</v>
+        <v>562546</v>
       </c>
       <c r="R7" t="n">
-        <v>6464940</v>
+        <v>6464954</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,17 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En hane i sitt häckningsrevir och födosöksområde</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,6 +1273,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1366,43 +1292,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113248963</v>
+        <v>122700417</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1410,13 +1334,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562504</v>
+        <v>562523</v>
       </c>
       <c r="R8" t="n">
-        <v>6464931</v>
+        <v>6464999</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,17 +1364,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Inne i av Södra planerad avverkningsanmälan A37222-23. Skoglig värdekärna V1 klassad av Länsstyrelsen.</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,15 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113249006</v>
+        <v>82059269</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,41 +1408,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Risten, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562498</v>
+        <v>562532</v>
       </c>
       <c r="R9" t="n">
-        <v>6464915</v>
+        <v>6464897</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,17 +1469,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Inne i av Södra planerad avverkningsanmälan A37222-23. Skoglig värdekärna V1 klassad av Länsstyrelsen</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,61 +1502,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113398077</v>
+        <v>129685021</v>
       </c>
       <c r="B10" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Björksveden, Björksveden, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562543</v>
+        <v>562526</v>
       </c>
       <c r="R10" t="n">
-        <v>6464911</v>
+        <v>6464898</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,17 +1567,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,27 +1587,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113544135</v>
+        <v>122700415</v>
       </c>
       <c r="B11" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,35 +1610,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1757,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562506</v>
+        <v>562546</v>
       </c>
       <c r="R11" t="n">
-        <v>6464936</v>
+        <v>6464954</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1787,17 +1667,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Paret som har sitt häckningsrevir och födosöksområde i området och I anslutning till torpet.</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,6 +1681,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1824,58 +1700,65 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115112531</v>
+        <v>115262867</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562494</v>
+        <v>562492</v>
       </c>
       <c r="R12" t="n">
-        <v>6464920</v>
+        <v>6464939</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,12 +1785,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Observerades inom häckningsrevir. De har börjat ifjol att häcka i området och dra upp en kull med ungar men nu hugger Södra myndigheternas goda mina bort viktigq delar av häckningsreviret.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1804,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1935,19 +1822,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113544064</v>
+        <v>113248919</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1968,26 +1850,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1995,13 +1861,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562522</v>
+        <v>562513</v>
       </c>
       <c r="R13" t="n">
-        <v>6464930</v>
+        <v>6464940</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,17 +1891,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hanen som har revir och födosöksområde i reservatsförslaget. Den brukar ses och höras i området nästan dagligen.</t>
+          <t>En hane i sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,32 +1928,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115262867</v>
+        <v>113398062</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2101,31 +1962,19 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562492</v>
+        <v>562494</v>
       </c>
       <c r="R14" t="n">
-        <v>6464939</v>
+        <v>6464971</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2152,17 +2001,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Observerades inom häckningsrevir. De har börjat ifjol att häcka i området och dra upp en kull med ungar men nu hugger Södra myndigheternas goda mina bort viktigq delar av häckningsreviret.</t>
+          <t>En hane som har revir och födosöksområde i området den syns och hörs typ dagligen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,6 +2035,1980 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113398088</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562525</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6464903</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nog samma hane som har revir här och sågs vid flera tillfällen tidigare</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113544064</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562522</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6464930</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hanen som har revir och födosöksområde i reservatsförslaget. Den brukar ses och höras i området nästan dagligen.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114919929</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562480</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6464895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Paret som håller till i området hade typ spelflygning och hördes mycket.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115112824</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>562558</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6464923</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 hanar och en hona som gjorde spelflyggningar under mycket ropande och tjadrande samt viss trummning</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113596175</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56822</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>562471</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6464903</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Har också observerats längre mot väster vid Nötebotjärnen och där sågs flera.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>92456297</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Åtvidaberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>562523</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6464941</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spår, äldre. Idag liggande träd.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115112754</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>562505</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6464906</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>110908846</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>562511</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6464967</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113249042</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562536</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6464923</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde som Södra tänker avverka. Gång på gång har man avverkad I reviret under falska förespeglingar om akuta barkborreangrepp men när man hugger på vintern finns inga  barkborrar längre i träden.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113398077</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562543</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6464911</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>113544135</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562506</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6464936</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Paret som har sitt häckningsrevir och födosöksområde i området och I anslutning till torpet.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129846531</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>562459</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6464927</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Revirparet</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110631484</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>562513</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6464945</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113248944</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>562513</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6464940</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Inne i av Södra planerad avverkningsanmälnan A37222-2023. Skoglig värdekärna klassat som V1 av Länsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113248963</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>562504</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6464931</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Inne i av Södra planerad avverkningsanmälan A37222-23. Skoglig värdekärna V1 klassad av Länsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113248976</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562492</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6464964</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Inne i av Södra planerad avverkningsanmälan A37222-2023. Skoglig värdekärna V1 klassad av Länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113249006</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>562498</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6464915</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inne i av Södra planerad avverkningsanmälan A37222-23. Skoglig värdekärna V1 klassad av Länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>115112531</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>562494</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6464920</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37222-2023 artfynd.xlsx
+++ b/artfynd/A 37222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68489160</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114920113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398085</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700414</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700417</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82059269</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700415</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115262867</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248919</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398062</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2145,6 +2215,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398088</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113544064</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114919929</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2495,6 +2580,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115112824</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2610,6 +2700,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113596175</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92456297</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2824,6 +2924,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115112754</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2925,6 +3030,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110908846</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113249042</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3141,6 +3256,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398077</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3255,6 +3375,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113544135</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3369,6 +3494,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129846531</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3475,6 +3605,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110631484</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3582,6 +3717,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248944</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3689,6 +3829,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248963</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3796,6 +3941,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248976</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3903,6 +4053,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113249006</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4009,8 +4164,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115112531</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>